--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132039461</v>
+        <v>132047474</v>
       </c>
       <c r="B2" t="n">
-        <v>5179</v>
+        <v>75423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634019</v>
+        <v>634083</v>
       </c>
       <c r="R2" t="n">
-        <v>6662594</v>
+        <v>6662868</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +775,7 @@
         <v>132039427</v>
       </c>
       <c r="B3" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132047474</v>
+        <v>132039461</v>
       </c>
       <c r="B4" t="n">
-        <v>75421</v>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634083</v>
+        <v>634019</v>
       </c>
       <c r="R4" t="n">
-        <v>6662868</v>
+        <v>6662594</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,9 +947,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -989,7 +989,7 @@
         <v>132039464</v>
       </c>
       <c r="B5" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132039482</v>
+        <v>132039470</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>91912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,23 +1211,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1235,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633998</v>
+        <v>634060</v>
       </c>
       <c r="R7" t="n">
-        <v>6663013</v>
+        <v>6662776</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1270,7 +1266,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,12 +1276,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,44 +1410,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132039470</v>
+        <v>132047471</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>75423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>634060</v>
+        <v>634056</v>
       </c>
       <c r="R9" t="n">
-        <v>6662776</v>
+        <v>6662736</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1483,19 +1478,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,60 +1495,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132047471</v>
+        <v>132039482</v>
       </c>
       <c r="B10" t="n">
-        <v>75421</v>
+        <v>57945</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>634056</v>
+        <v>633998</v>
       </c>
       <c r="R10" t="n">
-        <v>6662736</v>
+        <v>6663013</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,9 +1575,24 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,22 +1607,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132039448</v>
+        <v>132039425</v>
       </c>
       <c r="B11" t="n">
-        <v>57945</v>
+        <v>97338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>634024</v>
+        <v>634034</v>
       </c>
       <c r="R11" t="n">
-        <v>6662585</v>
+        <v>6663005</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1699,12 +1699,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1731,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132039425</v>
+        <v>132039448</v>
       </c>
       <c r="B12" t="n">
-        <v>97335</v>
+        <v>57945</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,21 +1737,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1766,13 +1761,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634034</v>
+        <v>634024</v>
       </c>
       <c r="R12" t="n">
-        <v>6663005</v>
+        <v>6662585</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1801,7 +1796,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1811,7 +1806,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132047466</v>
+        <v>132039449</v>
       </c>
       <c r="B13" t="n">
-        <v>96435</v>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634081</v>
+        <v>634019</v>
       </c>
       <c r="R13" t="n">
-        <v>6662733</v>
+        <v>6662585</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1906,9 +1906,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1923,22 +1933,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132039449</v>
+        <v>132047466</v>
       </c>
       <c r="B14" t="n">
-        <v>5179</v>
+        <v>96438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,37 +1956,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634019</v>
+        <v>634081</v>
       </c>
       <c r="R14" t="n">
-        <v>6662585</v>
+        <v>6662733</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2003,19 +2013,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2030,12 +2030,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
         <v>132039433</v>
       </c>
       <c r="B15" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>132039428</v>
       </c>
       <c r="B16" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>132047462</v>
       </c>
       <c r="B17" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>132039462</v>
       </c>
       <c r="B18" t="n">
-        <v>83287</v>
+        <v>83289</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>132039439</v>
       </c>
       <c r="B19" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>132039467</v>
       </c>
       <c r="B20" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>132039476</v>
       </c>
       <c r="B21" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>132039480</v>
       </c>
       <c r="B22" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>132039459</v>
       </c>
       <c r="B23" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,32 +3102,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132047469</v>
+        <v>132047464</v>
       </c>
       <c r="B25" t="n">
-        <v>75421</v>
+        <v>91892</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>634020</v>
+        <v>634050</v>
       </c>
       <c r="R25" t="n">
-        <v>6662596</v>
+        <v>6663000</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132039463</v>
+        <v>132047469</v>
       </c>
       <c r="B26" t="n">
-        <v>83278</v>
+        <v>75423</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3210,37 +3210,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>634032</v>
+        <v>634020</v>
       </c>
       <c r="R26" t="n">
-        <v>6662656</v>
+        <v>6662596</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3267,19 +3267,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3294,60 +3284,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132047464</v>
+        <v>132039463</v>
       </c>
       <c r="B27" t="n">
-        <v>91889</v>
+        <v>83280</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>634050</v>
+        <v>634032</v>
       </c>
       <c r="R27" t="n">
-        <v>6663000</v>
+        <v>6662656</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3374,9 +3364,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3391,12 +3391,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3406,7 +3406,7 @@
         <v>132039471</v>
       </c>
       <c r="B28" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>132039456</v>
       </c>
       <c r="B30" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>132047472</v>
       </c>
       <c r="B31" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>132039451</v>
       </c>
       <c r="B32" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>132047475</v>
       </c>
       <c r="B34" t="n">
-        <v>83278</v>
+        <v>83280</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>132047461</v>
       </c>
       <c r="B35" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>132047484</v>
       </c>
       <c r="B36" t="n">
-        <v>83287</v>
+        <v>83289</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>132047465</v>
       </c>
       <c r="B37" t="n">
-        <v>96435</v>
+        <v>96438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>132039452</v>
       </c>
       <c r="B38" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>132047468</v>
       </c>
       <c r="B39" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132047473</v>
+        <v>132048076</v>
       </c>
       <c r="B40" t="n">
-        <v>75421</v>
+        <v>58322</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4633,37 +4633,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>634107</v>
+        <v>634051</v>
       </c>
       <c r="R40" t="n">
-        <v>6662777</v>
+        <v>6662877</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4719,10 +4727,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132048076</v>
+        <v>132047473</v>
       </c>
       <c r="B41" t="n">
-        <v>58320</v>
+        <v>75423</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4730,45 +4738,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634051</v>
+        <v>634107</v>
       </c>
       <c r="R41" t="n">
-        <v>6662877</v>
+        <v>6662777</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4824,10 +4824,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132039455</v>
+        <v>132039472</v>
       </c>
       <c r="B42" t="n">
-        <v>75421</v>
+        <v>91855</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4835,21 +4835,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>634020</v>
+        <v>634029</v>
       </c>
       <c r="R42" t="n">
-        <v>6662606</v>
+        <v>6662867</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4931,10 +4931,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132039472</v>
+        <v>132039455</v>
       </c>
       <c r="B43" t="n">
-        <v>91852</v>
+        <v>75423</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4942,21 +4942,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4966,10 +4966,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>634029</v>
+        <v>634020</v>
       </c>
       <c r="R43" t="n">
-        <v>6662867</v>
+        <v>6662606</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5041,7 +5041,7 @@
         <v>132039444</v>
       </c>
       <c r="B44" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5145,10 +5145,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132047477</v>
+        <v>132039445</v>
       </c>
       <c r="B45" t="n">
-        <v>4781</v>
+        <v>75423</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5156,37 +5156,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>634094</v>
+        <v>634041</v>
       </c>
       <c r="R45" t="n">
-        <v>6662815</v>
+        <v>6662588</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5213,9 +5213,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5230,22 +5240,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132039450</v>
+        <v>132047477</v>
       </c>
       <c r="B46" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5253,37 +5263,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>634019</v>
+        <v>634094</v>
       </c>
       <c r="R46" t="n">
-        <v>6662585</v>
+        <v>6662815</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5310,19 +5320,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5337,44 +5337,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132039445</v>
+        <v>132039477</v>
       </c>
       <c r="B47" t="n">
-        <v>75421</v>
+        <v>57945</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>634041</v>
+        <v>634017</v>
       </c>
       <c r="R47" t="n">
-        <v>6662588</v>
+        <v>6662929</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5429,7 +5429,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5456,27 +5461,27 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132039477</v>
+        <v>132039450</v>
       </c>
       <c r="B48" t="n">
-        <v>57945</v>
+        <v>5199</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5491,13 +5496,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>634017</v>
+        <v>634019</v>
       </c>
       <c r="R48" t="n">
-        <v>6662929</v>
+        <v>6662585</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5526,7 +5531,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5536,12 +5541,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5678,7 +5678,7 @@
         <v>132039435</v>
       </c>
       <c r="B50" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>132047467</v>
       </c>
       <c r="B51" t="n">
-        <v>96437</v>
+        <v>96440</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>132039468</v>
       </c>
       <c r="B52" t="n">
-        <v>96437</v>
+        <v>96440</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>132230440</v>
       </c>
       <c r="B53" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6103,36 +6103,44 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132230442</v>
+        <v>132230444</v>
       </c>
       <c r="B54" t="n">
-        <v>99095</v>
+        <v>96534</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6142,10 +6150,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>634038</v>
+        <v>633998</v>
       </c>
       <c r="R54" t="n">
-        <v>6662583</v>
+        <v>6662610</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6178,11 +6186,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6210,44 +6213,36 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132230444</v>
+        <v>132230442</v>
       </c>
       <c r="B55" t="n">
-        <v>96531</v>
+        <v>99098</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6257,10 +6252,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>633998</v>
+        <v>634038</v>
       </c>
       <c r="R55" t="n">
-        <v>6662610</v>
+        <v>6662583</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6293,6 +6288,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6323,7 +6323,7 @@
         <v>132230447</v>
       </c>
       <c r="B56" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>132230445</v>
       </c>
       <c r="B57" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>132230439</v>
       </c>
       <c r="B58" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>132230443</v>
       </c>
       <c r="B59" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132039425</v>
+        <v>132039448</v>
       </c>
       <c r="B11" t="n">
-        <v>97338</v>
+        <v>57945</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>634034</v>
+        <v>634024</v>
       </c>
       <c r="R11" t="n">
-        <v>6663005</v>
+        <v>6662585</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1699,7 +1699,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1726,48 +1731,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132039448</v>
+        <v>132047466</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>96438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634024</v>
+        <v>634081</v>
       </c>
       <c r="R12" t="n">
-        <v>6662585</v>
+        <v>6662733</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,24 +1799,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,44 +1816,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132039449</v>
+        <v>132039425</v>
       </c>
       <c r="B13" t="n">
-        <v>5179</v>
+        <v>97338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1873,13 +1863,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634019</v>
+        <v>634034</v>
       </c>
       <c r="R13" t="n">
-        <v>6662585</v>
+        <v>6663005</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,7 +1898,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1918,7 +1908,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132047466</v>
+        <v>132039449</v>
       </c>
       <c r="B14" t="n">
-        <v>96438</v>
+        <v>5179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,37 +1946,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634081</v>
+        <v>634019</v>
       </c>
       <c r="R14" t="n">
-        <v>6662733</v>
+        <v>6662585</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2013,9 +2003,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2030,12 +2030,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2674,32 +2674,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132039476</v>
+        <v>132039459</v>
       </c>
       <c r="B21" t="n">
-        <v>97338</v>
+        <v>75423</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>634019</v>
+        <v>634045</v>
       </c>
       <c r="R21" t="n">
-        <v>6662926</v>
+        <v>6662589</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132039480</v>
+        <v>132039476</v>
       </c>
       <c r="B22" t="n">
-        <v>91892</v>
+        <v>97338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>634045</v>
+        <v>634019</v>
       </c>
       <c r="R22" t="n">
-        <v>6662998</v>
+        <v>6662926</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,32 +2888,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132039459</v>
+        <v>132039480</v>
       </c>
       <c r="B23" t="n">
-        <v>75423</v>
+        <v>91892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
         <v>634045</v>
       </c>
       <c r="R23" t="n">
-        <v>6662589</v>
+        <v>6662998</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3403,10 +3403,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132039471</v>
+        <v>132039453</v>
       </c>
       <c r="B28" t="n">
-        <v>97338</v>
+        <v>57945</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3414,21 +3414,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>634063</v>
+        <v>634000</v>
       </c>
       <c r="R28" t="n">
-        <v>6662830</v>
+        <v>6662604</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3483,7 +3483,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3510,10 +3515,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132039453</v>
+        <v>132039471</v>
       </c>
       <c r="B29" t="n">
-        <v>57945</v>
+        <v>97338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3521,21 +3526,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3545,10 +3550,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>634000</v>
+        <v>634063</v>
       </c>
       <c r="R29" t="n">
-        <v>6662604</v>
+        <v>6662830</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3580,7 +3585,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3590,12 +3595,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5145,32 +5145,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132039445</v>
+        <v>132039477</v>
       </c>
       <c r="B45" t="n">
-        <v>75423</v>
+        <v>57945</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5180,10 +5180,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>634041</v>
+        <v>634017</v>
       </c>
       <c r="R45" t="n">
-        <v>6662588</v>
+        <v>6662929</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5225,7 +5225,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5252,10 +5257,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132047477</v>
+        <v>132039450</v>
       </c>
       <c r="B46" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5263,37 +5268,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>634094</v>
+        <v>634019</v>
       </c>
       <c r="R46" t="n">
-        <v>6662815</v>
+        <v>6662585</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5320,9 +5325,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5337,44 +5352,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132039477</v>
+        <v>132039445</v>
       </c>
       <c r="B47" t="n">
-        <v>57945</v>
+        <v>75423</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5384,10 +5399,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>634017</v>
+        <v>634041</v>
       </c>
       <c r="R47" t="n">
-        <v>6662929</v>
+        <v>6662588</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5419,7 +5434,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5429,12 +5444,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5461,10 +5471,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132039450</v>
+        <v>132047477</v>
       </c>
       <c r="B48" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5472,37 +5482,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>634019</v>
+        <v>634094</v>
       </c>
       <c r="R48" t="n">
-        <v>6662585</v>
+        <v>6662815</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5529,19 +5539,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5556,12 +5556,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -2674,32 +2674,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132039459</v>
+        <v>132039476</v>
       </c>
       <c r="B21" t="n">
-        <v>75423</v>
+        <v>97338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>634045</v>
+        <v>634019</v>
       </c>
       <c r="R21" t="n">
-        <v>6662589</v>
+        <v>6662926</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132039476</v>
+        <v>132039480</v>
       </c>
       <c r="B22" t="n">
-        <v>97338</v>
+        <v>91892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>634019</v>
+        <v>634045</v>
       </c>
       <c r="R22" t="n">
-        <v>6662926</v>
+        <v>6662998</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,32 +2888,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132039480</v>
+        <v>132039459</v>
       </c>
       <c r="B23" t="n">
-        <v>91892</v>
+        <v>75423</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
         <v>634045</v>
       </c>
       <c r="R23" t="n">
-        <v>6662998</v>
+        <v>6662589</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3403,10 +3403,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132039453</v>
+        <v>132039471</v>
       </c>
       <c r="B28" t="n">
-        <v>57945</v>
+        <v>97338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3414,21 +3414,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>634000</v>
+        <v>634063</v>
       </c>
       <c r="R28" t="n">
-        <v>6662604</v>
+        <v>6662830</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3483,12 +3483,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3515,10 +3510,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132039471</v>
+        <v>132039453</v>
       </c>
       <c r="B29" t="n">
-        <v>97338</v>
+        <v>57945</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3526,21 +3521,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3550,10 +3545,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>634063</v>
+        <v>634000</v>
       </c>
       <c r="R29" t="n">
-        <v>6662830</v>
+        <v>6662604</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3585,7 +3580,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3595,7 +3590,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5145,32 +5145,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132039477</v>
+        <v>132039445</v>
       </c>
       <c r="B45" t="n">
-        <v>57945</v>
+        <v>75423</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5180,10 +5180,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>634017</v>
+        <v>634041</v>
       </c>
       <c r="R45" t="n">
-        <v>6662929</v>
+        <v>6662588</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5225,12 +5225,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5257,27 +5252,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132039450</v>
+        <v>132039477</v>
       </c>
       <c r="B46" t="n">
-        <v>5199</v>
+        <v>57945</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5292,13 +5287,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>634019</v>
+        <v>634017</v>
       </c>
       <c r="R46" t="n">
-        <v>6662585</v>
+        <v>6662929</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5327,7 +5322,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5337,7 +5332,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5364,10 +5364,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132039445</v>
+        <v>132047477</v>
       </c>
       <c r="B47" t="n">
-        <v>75423</v>
+        <v>4781</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5375,37 +5375,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>634041</v>
+        <v>634094</v>
       </c>
       <c r="R47" t="n">
-        <v>6662588</v>
+        <v>6662815</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5432,19 +5432,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5459,22 +5449,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132047477</v>
+        <v>132039450</v>
       </c>
       <c r="B48" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5482,37 +5472,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>634094</v>
+        <v>634019</v>
       </c>
       <c r="R48" t="n">
-        <v>6662815</v>
+        <v>6662585</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5539,9 +5529,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5556,12 +5556,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6417,44 +6417,36 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132230445</v>
+        <v>132230439</v>
       </c>
       <c r="B57" t="n">
-        <v>96534</v>
+        <v>99098</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6464,10 +6456,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>634018</v>
+        <v>633972</v>
       </c>
       <c r="R57" t="n">
-        <v>6663031</v>
+        <v>6663034</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6500,6 +6492,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6527,36 +6524,44 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132230439</v>
+        <v>132230445</v>
       </c>
       <c r="B58" t="n">
-        <v>99098</v>
+        <v>96534</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -6566,10 +6571,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>633972</v>
+        <v>634018</v>
       </c>
       <c r="R58" t="n">
-        <v>6663034</v>
+        <v>6663031</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6602,11 +6607,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132047474</v>
+        <v>132039461</v>
       </c>
       <c r="B2" t="n">
-        <v>75423</v>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634083</v>
+        <v>634019</v>
       </c>
       <c r="R2" t="n">
-        <v>6662868</v>
+        <v>6662594</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +743,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132039461</v>
+        <v>132047474</v>
       </c>
       <c r="B4" t="n">
-        <v>5179</v>
+        <v>75423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634019</v>
+        <v>634083</v>
       </c>
       <c r="R4" t="n">
-        <v>6662594</v>
+        <v>6662868</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,19 +957,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1200,44 +1200,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132039470</v>
+        <v>132047471</v>
       </c>
       <c r="B7" t="n">
-        <v>91912</v>
+        <v>75423</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634060</v>
+        <v>634056</v>
       </c>
       <c r="R7" t="n">
-        <v>6662776</v>
+        <v>6662736</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1264,19 +1268,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,46 +1285,42 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132039481</v>
+        <v>132039470</v>
       </c>
       <c r="B8" t="n">
-        <v>5179</v>
+        <v>91912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1338,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>634045</v>
+        <v>634060</v>
       </c>
       <c r="R8" t="n">
-        <v>6662998</v>
+        <v>6662776</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1373,7 +1363,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1383,7 +1373,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,48 +1400,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132047471</v>
+        <v>132039482</v>
       </c>
       <c r="B9" t="n">
-        <v>75423</v>
+        <v>57945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>634056</v>
+        <v>633998</v>
       </c>
       <c r="R9" t="n">
-        <v>6662736</v>
+        <v>6663013</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1478,9 +1468,24 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,44 +1500,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132039482</v>
+        <v>132039481</v>
       </c>
       <c r="B10" t="n">
-        <v>57945</v>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633998</v>
+        <v>634045</v>
       </c>
       <c r="R10" t="n">
-        <v>6663013</v>
+        <v>6662998</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1577,7 +1582,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1587,12 +1592,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,32 +1619,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132039448</v>
+        <v>132039449</v>
       </c>
       <c r="B11" t="n">
-        <v>57945</v>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>634024</v>
+        <v>634019</v>
       </c>
       <c r="R11" t="n">
         <v>6662585</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1699,12 +1699,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1731,48 +1726,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132047466</v>
+        <v>132039448</v>
       </c>
       <c r="B12" t="n">
-        <v>96438</v>
+        <v>57945</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634081</v>
+        <v>634024</v>
       </c>
       <c r="R12" t="n">
-        <v>6662733</v>
+        <v>6662585</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1799,9 +1794,24 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,12 +1826,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1935,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132039449</v>
+        <v>132047466</v>
       </c>
       <c r="B14" t="n">
-        <v>5179</v>
+        <v>96438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,37 +1956,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634019</v>
+        <v>634081</v>
       </c>
       <c r="R14" t="n">
-        <v>6662585</v>
+        <v>6662733</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2003,19 +2013,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2030,12 +2030,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2256,48 +2256,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132047462</v>
+        <v>132039467</v>
       </c>
       <c r="B17" t="n">
-        <v>97338</v>
+        <v>75423</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633997</v>
+        <v>634072</v>
       </c>
       <c r="R17" t="n">
-        <v>6662597</v>
+        <v>6662738</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2324,9 +2324,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2341,22 +2351,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132039462</v>
+        <v>132047462</v>
       </c>
       <c r="B18" t="n">
-        <v>83289</v>
+        <v>97338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2364,37 +2374,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>634032</v>
+        <v>633997</v>
       </c>
       <c r="R18" t="n">
-        <v>6662656</v>
+        <v>6662597</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2421,19 +2431,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2448,22 +2448,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132039439</v>
+        <v>132039462</v>
       </c>
       <c r="B19" t="n">
-        <v>97338</v>
+        <v>83289</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>634099</v>
+        <v>634032</v>
       </c>
       <c r="R19" t="n">
-        <v>6662755</v>
+        <v>6662656</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,32 +2567,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132039467</v>
+        <v>132039439</v>
       </c>
       <c r="B20" t="n">
-        <v>75423</v>
+        <v>97338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>634072</v>
+        <v>634099</v>
       </c>
       <c r="R20" t="n">
-        <v>6662738</v>
+        <v>6662755</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,32 +2781,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132039480</v>
+        <v>132039459</v>
       </c>
       <c r="B22" t="n">
-        <v>91892</v>
+        <v>75423</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
         <v>634045</v>
       </c>
       <c r="R22" t="n">
-        <v>6662998</v>
+        <v>6662589</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,32 +2888,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132039459</v>
+        <v>132039480</v>
       </c>
       <c r="B23" t="n">
-        <v>75423</v>
+        <v>91892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
         <v>634045</v>
       </c>
       <c r="R23" t="n">
-        <v>6662589</v>
+        <v>6662998</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,32 +3102,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132047464</v>
+        <v>132047469</v>
       </c>
       <c r="B25" t="n">
-        <v>91892</v>
+        <v>75423</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>634050</v>
+        <v>634020</v>
       </c>
       <c r="R25" t="n">
-        <v>6663000</v>
+        <v>6662596</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132047469</v>
+        <v>132039463</v>
       </c>
       <c r="B26" t="n">
-        <v>75423</v>
+        <v>83280</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3210,37 +3210,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>634020</v>
+        <v>634032</v>
       </c>
       <c r="R26" t="n">
-        <v>6662596</v>
+        <v>6662656</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3267,9 +3267,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3284,60 +3294,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132039463</v>
+        <v>132047464</v>
       </c>
       <c r="B27" t="n">
-        <v>83280</v>
+        <v>91892</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>634032</v>
+        <v>634050</v>
       </c>
       <c r="R27" t="n">
-        <v>6662656</v>
+        <v>6663000</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3364,19 +3374,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3391,22 +3391,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132039471</v>
+        <v>132039453</v>
       </c>
       <c r="B28" t="n">
-        <v>97338</v>
+        <v>57945</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3414,21 +3414,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>634063</v>
+        <v>634000</v>
       </c>
       <c r="R28" t="n">
-        <v>6662830</v>
+        <v>6662604</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3483,7 +3483,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3510,10 +3515,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132039453</v>
+        <v>132039471</v>
       </c>
       <c r="B29" t="n">
-        <v>57945</v>
+        <v>97338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3521,21 +3526,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3545,10 +3550,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>634000</v>
+        <v>634063</v>
       </c>
       <c r="R29" t="n">
-        <v>6662604</v>
+        <v>6662830</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3580,7 +3585,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3590,12 +3595,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4321,10 +4321,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132047465</v>
+        <v>132047468</v>
       </c>
       <c r="B37" t="n">
-        <v>96438</v>
+        <v>97963</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4332,21 +4332,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2818</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>634021</v>
+        <v>634099</v>
       </c>
       <c r="R37" t="n">
-        <v>6662610</v>
+        <v>6662776</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132039452</v>
+        <v>132047465</v>
       </c>
       <c r="B38" t="n">
-        <v>75423</v>
+        <v>96438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4429,37 +4429,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633999</v>
+        <v>634021</v>
       </c>
       <c r="R38" t="n">
-        <v>6662592</v>
+        <v>6662610</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4486,19 +4486,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4513,22 +4503,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132047468</v>
+        <v>132039452</v>
       </c>
       <c r="B39" t="n">
-        <v>97963</v>
+        <v>75423</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4536,37 +4526,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>634099</v>
+        <v>633999</v>
       </c>
       <c r="R39" t="n">
-        <v>6662776</v>
+        <v>6662592</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4593,9 +4583,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4610,22 +4610,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132048076</v>
+        <v>132047473</v>
       </c>
       <c r="B40" t="n">
-        <v>58322</v>
+        <v>75423</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4633,45 +4633,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>634051</v>
+        <v>634107</v>
       </c>
       <c r="R40" t="n">
-        <v>6662877</v>
+        <v>6662777</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4727,10 +4719,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132047473</v>
+        <v>132048076</v>
       </c>
       <c r="B41" t="n">
-        <v>75423</v>
+        <v>58322</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4738,37 +4730,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634107</v>
+        <v>634051</v>
       </c>
       <c r="R41" t="n">
-        <v>6662777</v>
+        <v>6662877</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -4824,10 +4824,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132039472</v>
+        <v>132039455</v>
       </c>
       <c r="B42" t="n">
-        <v>91855</v>
+        <v>75423</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4835,21 +4835,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>634029</v>
+        <v>634020</v>
       </c>
       <c r="R42" t="n">
-        <v>6662867</v>
+        <v>6662606</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4931,7 +4931,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132039455</v>
+        <v>132039444</v>
       </c>
       <c r="B43" t="n">
         <v>75423</v>
@@ -4966,10 +4966,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>634020</v>
+        <v>634042</v>
       </c>
       <c r="R43" t="n">
-        <v>6662606</v>
+        <v>6662585</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132039444</v>
+        <v>132039472</v>
       </c>
       <c r="B44" t="n">
-        <v>75423</v>
+        <v>91855</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,21 +5049,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>634042</v>
+        <v>634029</v>
       </c>
       <c r="R44" t="n">
-        <v>6662585</v>
+        <v>6662867</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -4824,10 +4824,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132039455</v>
+        <v>132039472</v>
       </c>
       <c r="B42" t="n">
-        <v>75423</v>
+        <v>91855</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4835,21 +4835,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>634020</v>
+        <v>634029</v>
       </c>
       <c r="R42" t="n">
-        <v>6662606</v>
+        <v>6662867</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4931,7 +4931,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132039444</v>
+        <v>132039455</v>
       </c>
       <c r="B43" t="n">
         <v>75423</v>
@@ -4966,10 +4966,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>634042</v>
+        <v>634020</v>
       </c>
       <c r="R43" t="n">
-        <v>6662585</v>
+        <v>6662606</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132039472</v>
+        <v>132039444</v>
       </c>
       <c r="B44" t="n">
-        <v>91855</v>
+        <v>75423</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,21 +5049,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>634029</v>
+        <v>634042</v>
       </c>
       <c r="R44" t="n">
-        <v>6662867</v>
+        <v>6662585</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6103,44 +6103,36 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132230444</v>
+        <v>132230442</v>
       </c>
       <c r="B54" t="n">
-        <v>96534</v>
+        <v>99098</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6150,10 +6142,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>633998</v>
+        <v>634038</v>
       </c>
       <c r="R54" t="n">
-        <v>6662610</v>
+        <v>6662583</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6186,6 +6178,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6213,36 +6210,44 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132230442</v>
+        <v>132230444</v>
       </c>
       <c r="B55" t="n">
-        <v>99098</v>
+        <v>96534</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6252,10 +6257,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>634038</v>
+        <v>633998</v>
       </c>
       <c r="R55" t="n">
-        <v>6662583</v>
+        <v>6662610</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6288,11 +6293,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -6103,36 +6103,44 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132230442</v>
+        <v>132230444</v>
       </c>
       <c r="B54" t="n">
-        <v>99098</v>
+        <v>96534</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6142,10 +6150,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>634038</v>
+        <v>633998</v>
       </c>
       <c r="R54" t="n">
-        <v>6662583</v>
+        <v>6662610</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6178,11 +6186,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6210,44 +6213,36 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132230444</v>
+        <v>132230442</v>
       </c>
       <c r="B55" t="n">
-        <v>96534</v>
+        <v>99098</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6257,10 +6252,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>633998</v>
+        <v>634038</v>
       </c>
       <c r="R55" t="n">
-        <v>6662610</v>
+        <v>6662583</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6293,6 +6288,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>132039427</v>
       </c>
       <c r="B3" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132047474</v>
       </c>
       <c r="B4" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>132039464</v>
       </c>
       <c r="B5" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,48 +1200,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132047471</v>
+        <v>132039470</v>
       </c>
       <c r="B7" t="n">
-        <v>75423</v>
+        <v>91918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634056</v>
+        <v>634060</v>
       </c>
       <c r="R7" t="n">
-        <v>6662736</v>
+        <v>6662776</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,9 +1264,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,56 +1291,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132039470</v>
+        <v>132047471</v>
       </c>
       <c r="B8" t="n">
-        <v>91912</v>
+        <v>75424</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>634060</v>
+        <v>634056</v>
       </c>
       <c r="R8" t="n">
-        <v>6662776</v>
+        <v>6662736</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,19 +1371,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,12 +1388,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
         <v>132039482</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,32 +1619,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132039449</v>
+        <v>132039425</v>
       </c>
       <c r="B11" t="n">
-        <v>5179</v>
+        <v>97346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>634019</v>
+        <v>634034</v>
       </c>
       <c r="R11" t="n">
-        <v>6662585</v>
+        <v>6663005</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1726,48 +1726,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132039448</v>
+        <v>132047466</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>96446</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634024</v>
+        <v>634081</v>
       </c>
       <c r="R12" t="n">
-        <v>6662585</v>
+        <v>6662733</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,24 +1794,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,22 +1811,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132039425</v>
+        <v>132039448</v>
       </c>
       <c r="B13" t="n">
-        <v>97338</v>
+        <v>57946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,21 +1834,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1873,13 +1858,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634034</v>
+        <v>634024</v>
       </c>
       <c r="R13" t="n">
-        <v>6663005</v>
+        <v>6662585</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,7 +1893,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1918,7 +1903,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132047466</v>
+        <v>132039449</v>
       </c>
       <c r="B14" t="n">
-        <v>96438</v>
+        <v>5179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,37 +1946,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634081</v>
+        <v>634019</v>
       </c>
       <c r="R14" t="n">
-        <v>6662733</v>
+        <v>6662585</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2013,9 +2003,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2030,12 +2030,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
         <v>132039433</v>
       </c>
       <c r="B15" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>132039428</v>
       </c>
       <c r="B16" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2256,32 +2256,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132039467</v>
+        <v>132039462</v>
       </c>
       <c r="B17" t="n">
-        <v>75423</v>
+        <v>83291</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634072</v>
+        <v>634032</v>
       </c>
       <c r="R17" t="n">
-        <v>6662738</v>
+        <v>6662656</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,10 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132047462</v>
+        <v>132039439</v>
       </c>
       <c r="B18" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2394,17 +2394,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633997</v>
+        <v>634099</v>
       </c>
       <c r="R18" t="n">
-        <v>6662597</v>
+        <v>6662755</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2431,9 +2431,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2448,22 +2458,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132039462</v>
+        <v>132047462</v>
       </c>
       <c r="B19" t="n">
-        <v>83289</v>
+        <v>97346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,37 +2481,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>634032</v>
+        <v>633997</v>
       </c>
       <c r="R19" t="n">
-        <v>6662656</v>
+        <v>6662597</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2528,19 +2538,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2555,44 +2555,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132039439</v>
+        <v>132039467</v>
       </c>
       <c r="B20" t="n">
-        <v>97338</v>
+        <v>75424</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>634099</v>
+        <v>634072</v>
       </c>
       <c r="R20" t="n">
-        <v>6662755</v>
+        <v>6662738</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132039476</v>
+        <v>132039480</v>
       </c>
       <c r="B21" t="n">
-        <v>97338</v>
+        <v>91898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>634019</v>
+        <v>634045</v>
       </c>
       <c r="R21" t="n">
-        <v>6662926</v>
+        <v>6662998</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2781,32 +2781,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132039459</v>
+        <v>132039476</v>
       </c>
       <c r="B22" t="n">
-        <v>75423</v>
+        <v>97346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>634045</v>
+        <v>634019</v>
       </c>
       <c r="R22" t="n">
-        <v>6662589</v>
+        <v>6662926</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,32 +2888,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132039480</v>
+        <v>132039459</v>
       </c>
       <c r="B23" t="n">
-        <v>91892</v>
+        <v>75424</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
         <v>634045</v>
       </c>
       <c r="R23" t="n">
-        <v>6662998</v>
+        <v>6662589</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,32 +3102,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132047469</v>
+        <v>132047464</v>
       </c>
       <c r="B25" t="n">
-        <v>75423</v>
+        <v>91898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>634020</v>
+        <v>634050</v>
       </c>
       <c r="R25" t="n">
-        <v>6662596</v>
+        <v>6663000</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132039463</v>
+        <v>132047469</v>
       </c>
       <c r="B26" t="n">
-        <v>83280</v>
+        <v>75424</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3210,37 +3210,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>634032</v>
+        <v>634020</v>
       </c>
       <c r="R26" t="n">
-        <v>6662656</v>
+        <v>6662596</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3267,19 +3267,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3294,60 +3284,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132047464</v>
+        <v>132039463</v>
       </c>
       <c r="B27" t="n">
-        <v>91892</v>
+        <v>83282</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>634050</v>
+        <v>634032</v>
       </c>
       <c r="R27" t="n">
-        <v>6663000</v>
+        <v>6662656</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3374,9 +3364,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3391,12 +3391,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3406,7 +3406,7 @@
         <v>132039453</v>
       </c>
       <c r="B28" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>132039471</v>
       </c>
       <c r="B29" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>132039456</v>
       </c>
       <c r="B30" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>132047472</v>
       </c>
       <c r="B31" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>132039451</v>
       </c>
       <c r="B32" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>132047475</v>
       </c>
       <c r="B34" t="n">
-        <v>83280</v>
+        <v>83282</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>132047461</v>
       </c>
       <c r="B35" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>132047484</v>
       </c>
       <c r="B36" t="n">
-        <v>83289</v>
+        <v>83291</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132047468</v>
+        <v>132047465</v>
       </c>
       <c r="B37" t="n">
-        <v>97963</v>
+        <v>96446</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4332,21 +4332,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>2818</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>634099</v>
+        <v>634021</v>
       </c>
       <c r="R37" t="n">
-        <v>6662776</v>
+        <v>6662610</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132047465</v>
+        <v>132039452</v>
       </c>
       <c r="B38" t="n">
-        <v>96438</v>
+        <v>75424</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4429,37 +4429,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>634021</v>
+        <v>633999</v>
       </c>
       <c r="R38" t="n">
-        <v>6662610</v>
+        <v>6662592</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4486,9 +4486,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4503,22 +4513,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132039452</v>
+        <v>132047468</v>
       </c>
       <c r="B39" t="n">
-        <v>75423</v>
+        <v>97971</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4526,37 +4536,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633999</v>
+        <v>634099</v>
       </c>
       <c r="R39" t="n">
-        <v>6662592</v>
+        <v>6662776</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4583,19 +4593,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4610,12 +4610,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4625,7 +4625,7 @@
         <v>132047473</v>
       </c>
       <c r="B40" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>132048076</v>
       </c>
       <c r="B41" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4824,10 +4824,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132039472</v>
+        <v>132039455</v>
       </c>
       <c r="B42" t="n">
-        <v>91855</v>
+        <v>75424</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4835,21 +4835,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>634029</v>
+        <v>634020</v>
       </c>
       <c r="R42" t="n">
-        <v>6662867</v>
+        <v>6662606</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4931,10 +4931,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132039455</v>
+        <v>132039444</v>
       </c>
       <c r="B43" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4966,10 +4966,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>634020</v>
+        <v>634042</v>
       </c>
       <c r="R43" t="n">
-        <v>6662606</v>
+        <v>6662585</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132039444</v>
+        <v>132039472</v>
       </c>
       <c r="B44" t="n">
-        <v>75423</v>
+        <v>91861</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,21 +5049,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>634042</v>
+        <v>634029</v>
       </c>
       <c r="R44" t="n">
-        <v>6662585</v>
+        <v>6662867</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5145,32 +5145,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132039445</v>
+        <v>132039477</v>
       </c>
       <c r="B45" t="n">
-        <v>75423</v>
+        <v>57946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5180,10 +5180,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>634041</v>
+        <v>634017</v>
       </c>
       <c r="R45" t="n">
-        <v>6662588</v>
+        <v>6662929</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5225,7 +5225,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5252,48 +5257,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132039477</v>
+        <v>132047477</v>
       </c>
       <c r="B46" t="n">
-        <v>57945</v>
+        <v>4781</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>634017</v>
+        <v>634094</v>
       </c>
       <c r="R46" t="n">
-        <v>6662929</v>
+        <v>6662815</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5320,24 +5325,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5352,22 +5342,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132047477</v>
+        <v>132039445</v>
       </c>
       <c r="B47" t="n">
-        <v>4781</v>
+        <v>75424</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5375,37 +5365,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>634094</v>
+        <v>634041</v>
       </c>
       <c r="R47" t="n">
-        <v>6662815</v>
+        <v>6662588</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5432,9 +5422,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5449,12 +5449,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5678,7 +5678,7 @@
         <v>132039435</v>
       </c>
       <c r="B50" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>132047467</v>
       </c>
       <c r="B51" t="n">
-        <v>96440</v>
+        <v>96448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>132039468</v>
       </c>
       <c r="B52" t="n">
-        <v>96440</v>
+        <v>96448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>132230440</v>
       </c>
       <c r="B53" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>132230444</v>
       </c>
       <c r="B54" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>132230442</v>
       </c>
       <c r="B55" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>132230447</v>
       </c>
       <c r="B56" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>132230439</v>
       </c>
       <c r="B57" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>132230445</v>
       </c>
       <c r="B58" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>132230443</v>
       </c>
       <c r="B59" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -4321,10 +4321,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132047465</v>
+        <v>132039452</v>
       </c>
       <c r="B37" t="n">
-        <v>96446</v>
+        <v>75424</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4332,37 +4332,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>634021</v>
+        <v>633999</v>
       </c>
       <c r="R37" t="n">
-        <v>6662610</v>
+        <v>6662592</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4389,9 +4389,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4406,22 +4416,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132039452</v>
+        <v>132047465</v>
       </c>
       <c r="B38" t="n">
-        <v>75424</v>
+        <v>96446</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4429,37 +4439,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633999</v>
+        <v>634021</v>
       </c>
       <c r="R38" t="n">
-        <v>6662592</v>
+        <v>6662610</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4486,19 +4496,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4513,12 +4513,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132047473</v>
+        <v>132048076</v>
       </c>
       <c r="B40" t="n">
-        <v>75424</v>
+        <v>58323</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4633,37 +4633,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>634107</v>
+        <v>634051</v>
       </c>
       <c r="R40" t="n">
-        <v>6662777</v>
+        <v>6662877</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4719,10 +4727,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132048076</v>
+        <v>132047473</v>
       </c>
       <c r="B41" t="n">
-        <v>58323</v>
+        <v>75424</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4730,45 +4738,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634051</v>
+        <v>634107</v>
       </c>
       <c r="R41" t="n">
-        <v>6662877</v>
+        <v>6662777</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5257,10 +5257,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132047477</v>
+        <v>132039445</v>
       </c>
       <c r="B46" t="n">
-        <v>4781</v>
+        <v>75424</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5268,37 +5268,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>634094</v>
+        <v>634041</v>
       </c>
       <c r="R46" t="n">
-        <v>6662815</v>
+        <v>6662588</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5325,9 +5325,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5342,22 +5352,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132039445</v>
+        <v>132047477</v>
       </c>
       <c r="B47" t="n">
-        <v>75424</v>
+        <v>4781</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5365,37 +5375,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>634041</v>
+        <v>634094</v>
       </c>
       <c r="R47" t="n">
-        <v>6662588</v>
+        <v>6662815</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5422,19 +5432,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5449,12 +5449,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132039461</v>
+        <v>132047474</v>
       </c>
       <c r="B2" t="n">
-        <v>5179</v>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634019</v>
+        <v>634083</v>
       </c>
       <c r="R2" t="n">
-        <v>6662594</v>
+        <v>6662868</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +775,7 @@
         <v>132039427</v>
       </c>
       <c r="B3" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132047474</v>
+        <v>132039461</v>
       </c>
       <c r="B4" t="n">
-        <v>75424</v>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634083</v>
+        <v>634019</v>
       </c>
       <c r="R4" t="n">
-        <v>6662868</v>
+        <v>6662594</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,9 +947,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -989,7 +989,7 @@
         <v>132039464</v>
       </c>
       <c r="B5" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>132039470</v>
       </c>
       <c r="B7" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,48 +1303,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132047471</v>
+        <v>132039482</v>
       </c>
       <c r="B8" t="n">
-        <v>75424</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>634056</v>
+        <v>633998</v>
       </c>
       <c r="R8" t="n">
-        <v>6662736</v>
+        <v>6663013</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1371,9 +1371,24 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,60 +1403,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132039482</v>
+        <v>132047471</v>
       </c>
       <c r="B9" t="n">
-        <v>57946</v>
+        <v>75428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633998</v>
+        <v>634056</v>
       </c>
       <c r="R9" t="n">
-        <v>6663013</v>
+        <v>6662736</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1468,24 +1483,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,12 +1500,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1622,7 +1622,7 @@
         <v>132039425</v>
       </c>
       <c r="B11" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132047466</v>
+        <v>132039449</v>
       </c>
       <c r="B12" t="n">
-        <v>96446</v>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1737,37 +1737,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634081</v>
+        <v>634019</v>
       </c>
       <c r="R12" t="n">
-        <v>6662733</v>
+        <v>6662585</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,9 +1794,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1811,60 +1821,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132039448</v>
+        <v>132047466</v>
       </c>
       <c r="B13" t="n">
-        <v>57946</v>
+        <v>96456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634024</v>
+        <v>634081</v>
       </c>
       <c r="R13" t="n">
-        <v>6662585</v>
+        <v>6662733</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,24 +1901,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1923,44 +1918,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132039449</v>
+        <v>132039448</v>
       </c>
       <c r="B14" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1970,13 +1965,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634019</v>
+        <v>634024</v>
       </c>
       <c r="R14" t="n">
         <v>6662585</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2005,7 +2000,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2015,7 +2010,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2045,7 +2045,7 @@
         <v>132039433</v>
       </c>
       <c r="B15" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>132039428</v>
       </c>
       <c r="B16" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2256,32 +2256,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132039462</v>
+        <v>132039467</v>
       </c>
       <c r="B17" t="n">
-        <v>83291</v>
+        <v>75428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634032</v>
+        <v>634072</v>
       </c>
       <c r="R17" t="n">
-        <v>6662656</v>
+        <v>6662738</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,10 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132039439</v>
+        <v>132047462</v>
       </c>
       <c r="B18" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2394,17 +2394,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>634099</v>
+        <v>633997</v>
       </c>
       <c r="R18" t="n">
-        <v>6662755</v>
+        <v>6662597</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2431,19 +2431,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2458,22 +2448,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132047462</v>
+        <v>132039462</v>
       </c>
       <c r="B19" t="n">
-        <v>97346</v>
+        <v>83299</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,37 +2471,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633997</v>
+        <v>634032</v>
       </c>
       <c r="R19" t="n">
-        <v>6662597</v>
+        <v>6662656</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2538,9 +2528,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2555,44 +2555,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132039467</v>
+        <v>132039439</v>
       </c>
       <c r="B20" t="n">
-        <v>75424</v>
+        <v>97356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>634072</v>
+        <v>634099</v>
       </c>
       <c r="R20" t="n">
-        <v>6662738</v>
+        <v>6662755</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2677,7 +2677,7 @@
         <v>132039480</v>
       </c>
       <c r="B21" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>132039476</v>
       </c>
       <c r="B22" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>132039459</v>
       </c>
       <c r="B23" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>132047464</v>
       </c>
       <c r="B25" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>132047469</v>
       </c>
       <c r="B26" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>132039463</v>
       </c>
       <c r="B27" t="n">
-        <v>83282</v>
+        <v>83290</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3403,10 +3403,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132039453</v>
+        <v>132039471</v>
       </c>
       <c r="B28" t="n">
-        <v>57946</v>
+        <v>97356</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3414,21 +3414,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>634000</v>
+        <v>634063</v>
       </c>
       <c r="R28" t="n">
-        <v>6662604</v>
+        <v>6662830</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3483,12 +3483,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3515,10 +3510,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132039471</v>
+        <v>132039453</v>
       </c>
       <c r="B29" t="n">
-        <v>97346</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3526,21 +3521,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3550,10 +3545,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>634063</v>
+        <v>634000</v>
       </c>
       <c r="R29" t="n">
-        <v>6662830</v>
+        <v>6662604</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3585,7 +3580,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3595,7 +3590,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3625,7 +3625,7 @@
         <v>132039456</v>
       </c>
       <c r="B30" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>132047472</v>
       </c>
       <c r="B31" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>132039451</v>
       </c>
       <c r="B32" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>132047475</v>
       </c>
       <c r="B34" t="n">
-        <v>83282</v>
+        <v>83290</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>132047461</v>
       </c>
       <c r="B35" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>132047484</v>
       </c>
       <c r="B36" t="n">
-        <v>83291</v>
+        <v>83299</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132039452</v>
+        <v>132047468</v>
       </c>
       <c r="B37" t="n">
-        <v>75424</v>
+        <v>97981</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4332,37 +4332,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633999</v>
+        <v>634099</v>
       </c>
       <c r="R37" t="n">
-        <v>6662592</v>
+        <v>6662776</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4389,19 +4389,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4416,12 +4406,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4431,7 +4421,7 @@
         <v>132047465</v>
       </c>
       <c r="B38" t="n">
-        <v>96446</v>
+        <v>96456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4525,10 +4515,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132047468</v>
+        <v>132039452</v>
       </c>
       <c r="B39" t="n">
-        <v>97971</v>
+        <v>75428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4536,37 +4526,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>634099</v>
+        <v>633999</v>
       </c>
       <c r="R39" t="n">
-        <v>6662776</v>
+        <v>6662592</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4593,9 +4583,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4610,22 +4610,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132048076</v>
+        <v>132047473</v>
       </c>
       <c r="B40" t="n">
-        <v>58323</v>
+        <v>75428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4633,45 +4633,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>634051</v>
+        <v>634107</v>
       </c>
       <c r="R40" t="n">
-        <v>6662877</v>
+        <v>6662777</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4727,10 +4719,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132047473</v>
+        <v>132048076</v>
       </c>
       <c r="B41" t="n">
-        <v>75424</v>
+        <v>58327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4738,37 +4730,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634107</v>
+        <v>634051</v>
       </c>
       <c r="R41" t="n">
-        <v>6662777</v>
+        <v>6662877</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>132039455</v>
       </c>
       <c r="B42" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>132039444</v>
       </c>
       <c r="B43" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>132039472</v>
       </c>
       <c r="B44" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5145,32 +5145,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132039477</v>
+        <v>132039445</v>
       </c>
       <c r="B45" t="n">
-        <v>57946</v>
+        <v>75428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5180,10 +5180,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>634017</v>
+        <v>634041</v>
       </c>
       <c r="R45" t="n">
-        <v>6662929</v>
+        <v>6662588</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5225,12 +5225,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5257,10 +5252,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132039445</v>
+        <v>132047477</v>
       </c>
       <c r="B46" t="n">
-        <v>75424</v>
+        <v>4781</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5268,37 +5263,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>634041</v>
+        <v>634094</v>
       </c>
       <c r="R46" t="n">
-        <v>6662588</v>
+        <v>6662815</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5325,19 +5320,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5352,60 +5337,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132047477</v>
+        <v>132039477</v>
       </c>
       <c r="B47" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>634094</v>
+        <v>634017</v>
       </c>
       <c r="R47" t="n">
-        <v>6662815</v>
+        <v>6662929</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5432,9 +5417,24 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5449,12 +5449,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5678,7 +5678,7 @@
         <v>132039435</v>
       </c>
       <c r="B50" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>132047467</v>
       </c>
       <c r="B51" t="n">
-        <v>96448</v>
+        <v>96458</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>132039468</v>
       </c>
       <c r="B52" t="n">
-        <v>96448</v>
+        <v>96458</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>132230440</v>
       </c>
       <c r="B53" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6103,44 +6103,36 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132230444</v>
+        <v>132230442</v>
       </c>
       <c r="B54" t="n">
-        <v>96542</v>
+        <v>99116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6150,10 +6142,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>633998</v>
+        <v>634038</v>
       </c>
       <c r="R54" t="n">
-        <v>6662610</v>
+        <v>6662583</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6186,6 +6178,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6213,36 +6210,44 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132230442</v>
+        <v>132230444</v>
       </c>
       <c r="B55" t="n">
-        <v>99106</v>
+        <v>96552</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6252,10 +6257,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>634038</v>
+        <v>633998</v>
       </c>
       <c r="R55" t="n">
-        <v>6662583</v>
+        <v>6662610</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6288,11 +6293,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6323,7 +6323,7 @@
         <v>132230447</v>
       </c>
       <c r="B56" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>132230439</v>
       </c>
       <c r="B57" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>132230445</v>
       </c>
       <c r="B58" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>132230443</v>
       </c>
       <c r="B59" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132039470</v>
+        <v>132039482</v>
       </c>
       <c r="B7" t="n">
-        <v>91928</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,19 +1211,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1231,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634060</v>
+        <v>633998</v>
       </c>
       <c r="R7" t="n">
-        <v>6662776</v>
+        <v>6663013</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1266,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1276,7 +1280,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132039482</v>
+        <v>132039470</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>91928</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,23 +1323,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1338,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633998</v>
+        <v>634060</v>
       </c>
       <c r="R8" t="n">
-        <v>6663013</v>
+        <v>6662776</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1373,7 +1378,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1383,12 +1388,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2674,32 +2674,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132039480</v>
+        <v>132039459</v>
       </c>
       <c r="B21" t="n">
-        <v>91908</v>
+        <v>75428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2712,7 +2712,7 @@
         <v>634045</v>
       </c>
       <c r="R21" t="n">
-        <v>6662998</v>
+        <v>6662589</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132039476</v>
+        <v>132039480</v>
       </c>
       <c r="B22" t="n">
-        <v>97356</v>
+        <v>91908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>634019</v>
+        <v>634045</v>
       </c>
       <c r="R22" t="n">
-        <v>6662926</v>
+        <v>6662998</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,32 +2888,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132039459</v>
+        <v>132039476</v>
       </c>
       <c r="B23" t="n">
-        <v>75428</v>
+        <v>97356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>634045</v>
+        <v>634019</v>
       </c>
       <c r="R23" t="n">
-        <v>6662589</v>
+        <v>6662926</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,32 +3102,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132047464</v>
+        <v>132047469</v>
       </c>
       <c r="B25" t="n">
-        <v>91908</v>
+        <v>75428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>634050</v>
+        <v>634020</v>
       </c>
       <c r="R25" t="n">
-        <v>6663000</v>
+        <v>6662596</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132047469</v>
+        <v>132039463</v>
       </c>
       <c r="B26" t="n">
-        <v>75428</v>
+        <v>83290</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3210,37 +3210,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>634020</v>
+        <v>634032</v>
       </c>
       <c r="R26" t="n">
-        <v>6662596</v>
+        <v>6662656</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3267,9 +3267,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3284,60 +3294,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132039463</v>
+        <v>132047464</v>
       </c>
       <c r="B27" t="n">
-        <v>83290</v>
+        <v>91908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>634032</v>
+        <v>634050</v>
       </c>
       <c r="R27" t="n">
-        <v>6662656</v>
+        <v>6663000</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3364,19 +3374,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3391,12 +3391,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132047468</v>
+        <v>132047465</v>
       </c>
       <c r="B37" t="n">
-        <v>97981</v>
+        <v>96456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4332,21 +4332,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>2818</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>634099</v>
+        <v>634021</v>
       </c>
       <c r="R37" t="n">
-        <v>6662776</v>
+        <v>6662610</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132047465</v>
+        <v>132039452</v>
       </c>
       <c r="B38" t="n">
-        <v>96456</v>
+        <v>75428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4429,37 +4429,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>634021</v>
+        <v>633999</v>
       </c>
       <c r="R38" t="n">
-        <v>6662610</v>
+        <v>6662592</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4486,9 +4486,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4503,22 +4513,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132039452</v>
+        <v>132047468</v>
       </c>
       <c r="B39" t="n">
-        <v>75428</v>
+        <v>97981</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4526,37 +4536,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633999</v>
+        <v>634099</v>
       </c>
       <c r="R39" t="n">
-        <v>6662592</v>
+        <v>6662776</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4583,19 +4593,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4610,22 +4610,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132047473</v>
+        <v>132048076</v>
       </c>
       <c r="B40" t="n">
-        <v>75428</v>
+        <v>58327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4633,37 +4633,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>634107</v>
+        <v>634051</v>
       </c>
       <c r="R40" t="n">
-        <v>6662777</v>
+        <v>6662877</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4719,10 +4727,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132048076</v>
+        <v>132047473</v>
       </c>
       <c r="B41" t="n">
-        <v>58327</v>
+        <v>75428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4730,45 +4738,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634051</v>
+        <v>634107</v>
       </c>
       <c r="R41" t="n">
-        <v>6662877</v>
+        <v>6662777</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>132039427</v>
       </c>
       <c r="B3" t="n">
-        <v>96552</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132039464</v>
+        <v>132039460</v>
       </c>
       <c r="B5" t="n">
-        <v>97356</v>
+        <v>8444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634048</v>
+        <v>634034</v>
       </c>
       <c r="R5" t="n">
-        <v>6662701</v>
+        <v>6662584</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132039460</v>
+        <v>132039464</v>
       </c>
       <c r="B6" t="n">
-        <v>8444</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634034</v>
+        <v>634048</v>
       </c>
       <c r="R6" t="n">
-        <v>6662584</v>
+        <v>6662701</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132039482</v>
+        <v>132039470</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>91929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,23 +1211,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1235,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633998</v>
+        <v>634060</v>
       </c>
       <c r="R7" t="n">
-        <v>6663013</v>
+        <v>6662776</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1270,7 +1266,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,12 +1276,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,30 +1303,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132039470</v>
+        <v>132039481</v>
       </c>
       <c r="B8" t="n">
-        <v>91928</v>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1343,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>634060</v>
+        <v>634045</v>
       </c>
       <c r="R8" t="n">
-        <v>6662776</v>
+        <v>6662998</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1378,7 +1373,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1388,7 +1383,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,48 +1410,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132047471</v>
+        <v>132039482</v>
       </c>
       <c r="B9" t="n">
-        <v>75428</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>634056</v>
+        <v>633998</v>
       </c>
       <c r="R9" t="n">
-        <v>6662736</v>
+        <v>6663013</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1483,9 +1478,24 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,22 +1510,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132039481</v>
+        <v>132047471</v>
       </c>
       <c r="B10" t="n">
-        <v>5179</v>
+        <v>75428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,37 +1533,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>634045</v>
+        <v>634056</v>
       </c>
       <c r="R10" t="n">
-        <v>6662998</v>
+        <v>6662736</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1580,19 +1590,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,12 +1607,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1622,7 +1622,7 @@
         <v>132039425</v>
       </c>
       <c r="B11" t="n">
-        <v>97356</v>
+        <v>97358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132039449</v>
+        <v>132047466</v>
       </c>
       <c r="B12" t="n">
-        <v>5179</v>
+        <v>96458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1737,37 +1737,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634019</v>
+        <v>634081</v>
       </c>
       <c r="R12" t="n">
-        <v>6662585</v>
+        <v>6662733</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,19 +1794,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1821,60 +1811,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132047466</v>
+        <v>132039448</v>
       </c>
       <c r="B13" t="n">
-        <v>96456</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634081</v>
+        <v>634024</v>
       </c>
       <c r="R13" t="n">
-        <v>6662733</v>
+        <v>6662585</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1901,9 +1891,24 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,44 +1923,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132039448</v>
+        <v>132039449</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>5179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1965,13 +1970,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634024</v>
+        <v>634019</v>
       </c>
       <c r="R14" t="n">
         <v>6662585</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2000,7 +2005,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2010,12 +2015,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,32 +2256,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132039467</v>
+        <v>132039462</v>
       </c>
       <c r="B17" t="n">
-        <v>75428</v>
+        <v>83299</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634072</v>
+        <v>634032</v>
       </c>
       <c r="R17" t="n">
-        <v>6662738</v>
+        <v>6662656</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,7 +2366,7 @@
         <v>132047462</v>
       </c>
       <c r="B18" t="n">
-        <v>97356</v>
+        <v>97358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132039462</v>
+        <v>132039439</v>
       </c>
       <c r="B19" t="n">
-        <v>83299</v>
+        <v>97358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>634032</v>
+        <v>634099</v>
       </c>
       <c r="R19" t="n">
-        <v>6662656</v>
+        <v>6662755</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,32 +2567,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132039439</v>
+        <v>132039467</v>
       </c>
       <c r="B20" t="n">
-        <v>97356</v>
+        <v>75428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>634099</v>
+        <v>634072</v>
       </c>
       <c r="R20" t="n">
-        <v>6662755</v>
+        <v>6662738</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2674,32 +2674,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132039459</v>
+        <v>132039476</v>
       </c>
       <c r="B21" t="n">
-        <v>75428</v>
+        <v>97358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>634045</v>
+        <v>634019</v>
       </c>
       <c r="R21" t="n">
-        <v>6662589</v>
+        <v>6662926</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2781,32 +2781,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132039480</v>
+        <v>132039459</v>
       </c>
       <c r="B22" t="n">
-        <v>91908</v>
+        <v>75428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
         <v>634045</v>
       </c>
       <c r="R22" t="n">
-        <v>6662998</v>
+        <v>6662589</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,10 +2888,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132039476</v>
+        <v>132039480</v>
       </c>
       <c r="B23" t="n">
-        <v>97356</v>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2899,21 +2899,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>634019</v>
+        <v>634045</v>
       </c>
       <c r="R23" t="n">
-        <v>6662926</v>
+        <v>6662998</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3309,7 +3309,7 @@
         <v>132047464</v>
       </c>
       <c r="B27" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3403,10 +3403,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132039471</v>
+        <v>132039453</v>
       </c>
       <c r="B28" t="n">
-        <v>97356</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3414,21 +3414,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>634063</v>
+        <v>634000</v>
       </c>
       <c r="R28" t="n">
-        <v>6662830</v>
+        <v>6662604</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3483,7 +3483,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3510,10 +3515,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132039453</v>
+        <v>132039471</v>
       </c>
       <c r="B29" t="n">
-        <v>57950</v>
+        <v>97358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3521,21 +3526,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3545,10 +3550,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>634000</v>
+        <v>634063</v>
       </c>
       <c r="R29" t="n">
-        <v>6662604</v>
+        <v>6662830</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3580,7 +3585,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3590,12 +3595,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4130,7 +4130,7 @@
         <v>132047461</v>
       </c>
       <c r="B35" t="n">
-        <v>97356</v>
+        <v>97358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>132047465</v>
       </c>
       <c r="B37" t="n">
-        <v>96456</v>
+        <v>96458</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132039452</v>
+        <v>132047468</v>
       </c>
       <c r="B38" t="n">
-        <v>75428</v>
+        <v>97983</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4429,37 +4429,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6426</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633999</v>
+        <v>634099</v>
       </c>
       <c r="R38" t="n">
-        <v>6662592</v>
+        <v>6662776</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4486,19 +4486,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4513,22 +4503,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132047468</v>
+        <v>132039452</v>
       </c>
       <c r="B39" t="n">
-        <v>97981</v>
+        <v>75428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4536,37 +4526,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>634099</v>
+        <v>633999</v>
       </c>
       <c r="R39" t="n">
-        <v>6662776</v>
+        <v>6662592</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4593,9 +4583,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4610,22 +4610,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132048076</v>
+        <v>132047473</v>
       </c>
       <c r="B40" t="n">
-        <v>58327</v>
+        <v>75428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4633,45 +4633,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>634051</v>
+        <v>634107</v>
       </c>
       <c r="R40" t="n">
-        <v>6662877</v>
+        <v>6662777</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4727,10 +4719,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132047473</v>
+        <v>132048076</v>
       </c>
       <c r="B41" t="n">
-        <v>75428</v>
+        <v>58327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4738,37 +4730,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634107</v>
+        <v>634051</v>
       </c>
       <c r="R41" t="n">
-        <v>6662777</v>
+        <v>6662877</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>132039472</v>
       </c>
       <c r="B44" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>132047467</v>
       </c>
       <c r="B51" t="n">
-        <v>96458</v>
+        <v>96460</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>132039468</v>
       </c>
       <c r="B52" t="n">
-        <v>96458</v>
+        <v>96460</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>132230440</v>
       </c>
       <c r="B53" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6103,36 +6103,44 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132230442</v>
+        <v>132230444</v>
       </c>
       <c r="B54" t="n">
-        <v>99116</v>
+        <v>96554</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6142,10 +6150,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>634038</v>
+        <v>633998</v>
       </c>
       <c r="R54" t="n">
-        <v>6662583</v>
+        <v>6662610</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6178,11 +6186,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6210,44 +6213,36 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132230444</v>
+        <v>132230442</v>
       </c>
       <c r="B55" t="n">
-        <v>96552</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6257,10 +6252,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>633998</v>
+        <v>634038</v>
       </c>
       <c r="R55" t="n">
-        <v>6662610</v>
+        <v>6662583</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6293,6 +6288,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6323,7 +6323,7 @@
         <v>132230447</v>
       </c>
       <c r="B56" t="n">
-        <v>101323</v>
+        <v>101325</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6417,36 +6417,44 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132230439</v>
+        <v>132230445</v>
       </c>
       <c r="B57" t="n">
-        <v>99116</v>
+        <v>96554</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6456,10 +6464,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>633972</v>
+        <v>634018</v>
       </c>
       <c r="R57" t="n">
-        <v>6663034</v>
+        <v>6663031</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6492,11 +6500,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6524,44 +6527,36 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132230445</v>
+        <v>132230439</v>
       </c>
       <c r="B58" t="n">
-        <v>96552</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -6571,10 +6566,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>634018</v>
+        <v>633972</v>
       </c>
       <c r="R58" t="n">
-        <v>6663031</v>
+        <v>6663034</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6607,6 +6602,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6637,7 +6637,7 @@
         <v>132230443</v>
       </c>
       <c r="B59" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132039460</v>
+        <v>132039464</v>
       </c>
       <c r="B5" t="n">
-        <v>8444</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634034</v>
+        <v>634048</v>
       </c>
       <c r="R5" t="n">
-        <v>6662584</v>
+        <v>6662701</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132039464</v>
+        <v>132039460</v>
       </c>
       <c r="B6" t="n">
-        <v>97358</v>
+        <v>8444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634048</v>
+        <v>634034</v>
       </c>
       <c r="R6" t="n">
-        <v>6662701</v>
+        <v>6662584</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,44 +1200,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132039470</v>
+        <v>132047471</v>
       </c>
       <c r="B7" t="n">
-        <v>91929</v>
+        <v>75428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634060</v>
+        <v>634056</v>
       </c>
       <c r="R7" t="n">
-        <v>6662776</v>
+        <v>6662736</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1264,19 +1268,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,46 +1285,42 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132039481</v>
+        <v>132039470</v>
       </c>
       <c r="B8" t="n">
-        <v>5179</v>
+        <v>91929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1338,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>634045</v>
+        <v>634060</v>
       </c>
       <c r="R8" t="n">
-        <v>6662998</v>
+        <v>6662776</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1373,7 +1363,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1383,7 +1373,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,32 +1400,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132039482</v>
+        <v>132039481</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1435,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633998</v>
+        <v>634045</v>
       </c>
       <c r="R9" t="n">
-        <v>6663013</v>
+        <v>6662998</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1480,7 +1470,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1490,12 +1480,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,48 +1507,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132047471</v>
+        <v>132039482</v>
       </c>
       <c r="B10" t="n">
-        <v>75428</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>634056</v>
+        <v>633998</v>
       </c>
       <c r="R10" t="n">
-        <v>6662736</v>
+        <v>6663013</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,9 +1575,24 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,12 +1607,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132039453</v>
+        <v>132039471</v>
       </c>
       <c r="B28" t="n">
-        <v>57950</v>
+        <v>97358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3414,21 +3414,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>634000</v>
+        <v>634063</v>
       </c>
       <c r="R28" t="n">
-        <v>6662604</v>
+        <v>6662830</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3483,12 +3483,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3515,10 +3510,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132039471</v>
+        <v>132039453</v>
       </c>
       <c r="B29" t="n">
-        <v>97358</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3526,21 +3521,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3550,10 +3545,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>634063</v>
+        <v>634000</v>
       </c>
       <c r="R29" t="n">
-        <v>6662830</v>
+        <v>6662604</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3585,7 +3580,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3595,7 +3590,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4321,10 +4321,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132047465</v>
+        <v>132039452</v>
       </c>
       <c r="B37" t="n">
-        <v>96458</v>
+        <v>75428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4332,37 +4332,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>634021</v>
+        <v>633999</v>
       </c>
       <c r="R37" t="n">
-        <v>6662610</v>
+        <v>6662592</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4389,9 +4389,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4406,22 +4416,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132047468</v>
+        <v>132047465</v>
       </c>
       <c r="B38" t="n">
-        <v>97983</v>
+        <v>96458</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4429,21 +4439,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4453,10 +4463,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>634099</v>
+        <v>634021</v>
       </c>
       <c r="R38" t="n">
-        <v>6662776</v>
+        <v>6662610</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4515,10 +4525,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132039452</v>
+        <v>132047468</v>
       </c>
       <c r="B39" t="n">
-        <v>75428</v>
+        <v>97983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4526,37 +4536,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633999</v>
+        <v>634099</v>
       </c>
       <c r="R39" t="n">
-        <v>6662592</v>
+        <v>6662776</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4583,19 +4593,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4610,22 +4610,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132047473</v>
+        <v>132048076</v>
       </c>
       <c r="B40" t="n">
-        <v>75428</v>
+        <v>58327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4633,37 +4633,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>634107</v>
+        <v>634051</v>
       </c>
       <c r="R40" t="n">
-        <v>6662777</v>
+        <v>6662877</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4719,10 +4727,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132048076</v>
+        <v>132047473</v>
       </c>
       <c r="B41" t="n">
-        <v>58327</v>
+        <v>75428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4730,45 +4738,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634051</v>
+        <v>634107</v>
       </c>
       <c r="R41" t="n">
-        <v>6662877</v>
+        <v>6662777</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5252,48 +5252,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132047477</v>
+        <v>132039477</v>
       </c>
       <c r="B46" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>634094</v>
+        <v>634017</v>
       </c>
       <c r="R46" t="n">
-        <v>6662815</v>
+        <v>6662929</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5320,9 +5320,24 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5337,60 +5352,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132039477</v>
+        <v>132047477</v>
       </c>
       <c r="B47" t="n">
-        <v>57950</v>
+        <v>4781</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>634017</v>
+        <v>634094</v>
       </c>
       <c r="R47" t="n">
-        <v>6662929</v>
+        <v>6662815</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5417,24 +5432,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5449,12 +5449,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132047474</v>
+        <v>132039427</v>
       </c>
       <c r="B2" t="n">
-        <v>75428</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634083</v>
+        <v>634057</v>
       </c>
       <c r="R2" t="n">
-        <v>6662868</v>
+        <v>6662980</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +743,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132039427</v>
+        <v>132047474</v>
       </c>
       <c r="B3" t="n">
-        <v>96554</v>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634057</v>
+        <v>634083</v>
       </c>
       <c r="R3" t="n">
-        <v>6662980</v>
+        <v>6662868</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -840,19 +850,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132047471</v>
+        <v>132039481</v>
       </c>
       <c r="B7" t="n">
-        <v>75428</v>
+        <v>5179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,37 +1211,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634056</v>
+        <v>634045</v>
       </c>
       <c r="R7" t="n">
-        <v>6662736</v>
+        <v>6662998</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,9 +1268,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1295,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1400,32 +1410,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132039481</v>
+        <v>132039482</v>
       </c>
       <c r="B9" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1435,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>634045</v>
+        <v>633998</v>
       </c>
       <c r="R9" t="n">
-        <v>6662998</v>
+        <v>6663013</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1470,7 +1480,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1480,7 +1490,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1507,48 +1522,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132039482</v>
+        <v>132047471</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>75428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633998</v>
+        <v>634056</v>
       </c>
       <c r="R10" t="n">
-        <v>6663013</v>
+        <v>6662736</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1575,24 +1590,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,12 +1607,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132039462</v>
+        <v>132047462</v>
       </c>
       <c r="B17" t="n">
-        <v>83299</v>
+        <v>97358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2267,37 +2267,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634032</v>
+        <v>633997</v>
       </c>
       <c r="R17" t="n">
-        <v>6662656</v>
+        <v>6662597</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2324,19 +2324,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,22 +2341,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132047462</v>
+        <v>132039462</v>
       </c>
       <c r="B18" t="n">
-        <v>97358</v>
+        <v>83299</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,37 +2364,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633997</v>
+        <v>634032</v>
       </c>
       <c r="R18" t="n">
-        <v>6662597</v>
+        <v>6662656</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2431,9 +2421,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2448,12 +2448,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132039476</v>
+        <v>132039480</v>
       </c>
       <c r="B21" t="n">
-        <v>97358</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>634019</v>
+        <v>634045</v>
       </c>
       <c r="R21" t="n">
-        <v>6662926</v>
+        <v>6662998</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2781,32 +2781,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132039459</v>
+        <v>132039476</v>
       </c>
       <c r="B22" t="n">
-        <v>75428</v>
+        <v>97358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>634045</v>
+        <v>634019</v>
       </c>
       <c r="R22" t="n">
-        <v>6662589</v>
+        <v>6662926</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,32 +2888,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132039480</v>
+        <v>132039459</v>
       </c>
       <c r="B23" t="n">
-        <v>91909</v>
+        <v>75428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
         <v>634045</v>
       </c>
       <c r="R23" t="n">
-        <v>6662998</v>
+        <v>6662589</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3622,10 +3622,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132039456</v>
+        <v>132047485</v>
       </c>
       <c r="B30" t="n">
-        <v>75428</v>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3633,37 +3633,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>634037</v>
+        <v>634079</v>
       </c>
       <c r="R30" t="n">
-        <v>6662606</v>
+        <v>6662720</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3690,19 +3690,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,19 +3707,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132047472</v>
+        <v>132039456</v>
       </c>
       <c r="B31" t="n">
         <v>75428</v>
@@ -3760,17 +3750,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>634101</v>
+        <v>634037</v>
       </c>
       <c r="R31" t="n">
-        <v>6662784</v>
+        <v>6662606</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3797,9 +3787,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3814,19 +3814,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132039451</v>
+        <v>132047472</v>
       </c>
       <c r="B32" t="n">
         <v>75428</v>
@@ -3857,17 +3857,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>634007</v>
+        <v>634101</v>
       </c>
       <c r="R32" t="n">
-        <v>6662592</v>
+        <v>6662784</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3894,19 +3894,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3921,22 +3911,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132047485</v>
+        <v>132039451</v>
       </c>
       <c r="B33" t="n">
-        <v>5179</v>
+        <v>75428</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3944,37 +3934,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>634079</v>
+        <v>634007</v>
       </c>
       <c r="R33" t="n">
-        <v>6662720</v>
+        <v>6662592</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4001,9 +3991,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4018,12 +4018,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132039452</v>
+        <v>132047465</v>
       </c>
       <c r="B37" t="n">
-        <v>75428</v>
+        <v>96458</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4332,37 +4332,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633999</v>
+        <v>634021</v>
       </c>
       <c r="R37" t="n">
-        <v>6662592</v>
+        <v>6662610</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4389,19 +4389,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4416,22 +4406,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132047465</v>
+        <v>132039452</v>
       </c>
       <c r="B38" t="n">
-        <v>96458</v>
+        <v>75428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4439,37 +4429,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>634021</v>
+        <v>633999</v>
       </c>
       <c r="R38" t="n">
-        <v>6662610</v>
+        <v>6662592</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4496,9 +4486,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4513,12 +4513,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132048076</v>
+        <v>132047473</v>
       </c>
       <c r="B40" t="n">
-        <v>58327</v>
+        <v>75428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4633,45 +4633,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>634051</v>
+        <v>634107</v>
       </c>
       <c r="R40" t="n">
-        <v>6662877</v>
+        <v>6662777</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4727,10 +4719,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132047473</v>
+        <v>132048076</v>
       </c>
       <c r="B41" t="n">
-        <v>75428</v>
+        <v>58327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4738,37 +4730,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen, ost, Åkerlänna-Marstalla, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>634107</v>
+        <v>634051</v>
       </c>
       <c r="R41" t="n">
-        <v>6662777</v>
+        <v>6662877</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4824,10 +4824,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132039455</v>
+        <v>132039472</v>
       </c>
       <c r="B42" t="n">
-        <v>75428</v>
+        <v>91872</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4835,21 +4835,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>634020</v>
+        <v>634029</v>
       </c>
       <c r="R42" t="n">
-        <v>6662606</v>
+        <v>6662867</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4931,7 +4931,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132039444</v>
+        <v>132039455</v>
       </c>
       <c r="B43" t="n">
         <v>75428</v>
@@ -4966,10 +4966,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>634042</v>
+        <v>634020</v>
       </c>
       <c r="R43" t="n">
-        <v>6662585</v>
+        <v>6662606</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132039472</v>
+        <v>132039444</v>
       </c>
       <c r="B44" t="n">
-        <v>91872</v>
+        <v>75428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,21 +5049,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>634029</v>
+        <v>634042</v>
       </c>
       <c r="R44" t="n">
-        <v>6662867</v>
+        <v>6662585</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5145,32 +5145,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132039445</v>
+        <v>132039477</v>
       </c>
       <c r="B45" t="n">
-        <v>75428</v>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5180,10 +5180,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>634041</v>
+        <v>634017</v>
       </c>
       <c r="R45" t="n">
-        <v>6662588</v>
+        <v>6662929</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5225,7 +5225,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5252,32 +5257,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132039477</v>
+        <v>132039445</v>
       </c>
       <c r="B46" t="n">
-        <v>57950</v>
+        <v>75428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5287,10 +5292,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>634017</v>
+        <v>634041</v>
       </c>
       <c r="R46" t="n">
-        <v>6662929</v>
+        <v>6662588</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5322,7 +5327,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5332,12 +5337,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6323,7 +6323,7 @@
         <v>132230447</v>
       </c>
       <c r="B56" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -3622,10 +3622,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132047485</v>
+        <v>132039456</v>
       </c>
       <c r="B30" t="n">
-        <v>5179</v>
+        <v>75428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3633,37 +3633,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>634079</v>
+        <v>634037</v>
       </c>
       <c r="R30" t="n">
-        <v>6662720</v>
+        <v>6662606</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3690,9 +3690,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3707,19 +3717,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132039456</v>
+        <v>132047472</v>
       </c>
       <c r="B31" t="n">
         <v>75428</v>
@@ -3750,17 +3760,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>634037</v>
+        <v>634101</v>
       </c>
       <c r="R31" t="n">
-        <v>6662606</v>
+        <v>6662784</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3787,19 +3797,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3814,19 +3814,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132047472</v>
+        <v>132039451</v>
       </c>
       <c r="B32" t="n">
         <v>75428</v>
@@ -3857,17 +3857,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tvigölingen, ost, Upl</t>
+          <t>Tvigölingen Ost, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>634101</v>
+        <v>634007</v>
       </c>
       <c r="R32" t="n">
-        <v>6662784</v>
+        <v>6662592</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3894,9 +3894,19 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3911,22 +3921,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132039451</v>
+        <v>132047485</v>
       </c>
       <c r="B33" t="n">
-        <v>75428</v>
+        <v>5179</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3934,37 +3944,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tvigölingen Ost, Upl</t>
+          <t>Tvigölingen, ost, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>634007</v>
+        <v>634079</v>
       </c>
       <c r="R33" t="n">
-        <v>6662592</v>
+        <v>6662720</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3991,19 +4001,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4018,12 +4018,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -6103,44 +6103,36 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132230444</v>
+        <v>132230442</v>
       </c>
       <c r="B54" t="n">
-        <v>96554</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6150,10 +6142,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>633998</v>
+        <v>634038</v>
       </c>
       <c r="R54" t="n">
-        <v>6662610</v>
+        <v>6662583</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6186,6 +6178,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6213,36 +6210,44 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132230442</v>
+        <v>132230444</v>
       </c>
       <c r="B55" t="n">
-        <v>99118</v>
+        <v>96554</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6252,10 +6257,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>634038</v>
+        <v>633998</v>
       </c>
       <c r="R55" t="n">
-        <v>6662583</v>
+        <v>6662610</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6288,11 +6293,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6417,44 +6417,36 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132230445</v>
+        <v>132230439</v>
       </c>
       <c r="B57" t="n">
-        <v>96554</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6464,10 +6456,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>634018</v>
+        <v>633972</v>
       </c>
       <c r="R57" t="n">
-        <v>6663031</v>
+        <v>6663034</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6500,6 +6492,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6527,36 +6524,44 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132230439</v>
+        <v>132230445</v>
       </c>
       <c r="B58" t="n">
-        <v>99118</v>
+        <v>96554</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -6566,10 +6571,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>633972</v>
+        <v>634018</v>
       </c>
       <c r="R58" t="n">
-        <v>6663034</v>
+        <v>6663031</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6602,11 +6607,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 60269-2025 artfynd.xlsx
+++ b/artfynd/A 60269-2025 artfynd.xlsx
@@ -5785,7 +5785,7 @@
         <v>132047467</v>
       </c>
       <c r="B51" t="n">
-        <v>96460</v>
+        <v>96461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>132039468</v>
       </c>
       <c r="B52" t="n">
-        <v>96460</v>
+        <v>96461</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>132230440</v>
       </c>
       <c r="B53" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6103,36 +6103,44 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132230442</v>
+        <v>132230444</v>
       </c>
       <c r="B54" t="n">
-        <v>99118</v>
+        <v>96555</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6142,10 +6150,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>634038</v>
+        <v>633998</v>
       </c>
       <c r="R54" t="n">
-        <v>6662583</v>
+        <v>6662610</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6178,11 +6186,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6210,44 +6213,36 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132230444</v>
+        <v>132230442</v>
       </c>
       <c r="B55" t="n">
-        <v>96554</v>
+        <v>99119</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6257,10 +6252,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>633998</v>
+        <v>634038</v>
       </c>
       <c r="R55" t="n">
-        <v>6662610</v>
+        <v>6662583</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6293,6 +6288,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>6 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6323,7 +6323,7 @@
         <v>132230447</v>
       </c>
       <c r="B56" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6417,36 +6417,44 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132230439</v>
+        <v>132230445</v>
       </c>
       <c r="B57" t="n">
-        <v>99118</v>
+        <v>96555</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6456,10 +6464,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>633972</v>
+        <v>634018</v>
       </c>
       <c r="R57" t="n">
-        <v>6663034</v>
+        <v>6663031</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6492,11 +6500,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6524,44 +6527,36 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132230445</v>
+        <v>132230439</v>
       </c>
       <c r="B58" t="n">
-        <v>96554</v>
+        <v>99119</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -6571,10 +6566,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>634018</v>
+        <v>633972</v>
       </c>
       <c r="R58" t="n">
-        <v>6663031</v>
+        <v>6663034</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6607,6 +6602,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6637,7 +6637,7 @@
         <v>132230443</v>
       </c>
       <c r="B59" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
